--- a/Filtered/HCAFlorida_Kendall_Hospital.xlsx
+++ b/Filtered/HCAFlorida_Kendall_Hospital.xlsx
@@ -574,6 +574,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -626,6 +636,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -698,6 +718,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -750,6 +780,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -822,6 +862,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -874,6 +924,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -946,6 +1006,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -998,6 +1068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1070,6 +1150,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1122,6 +1212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1194,6 +1294,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1266,6 +1376,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1318,6 +1438,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1390,6 +1520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1442,6 +1582,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1514,6 +1664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1566,6 +1726,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1638,6 +1808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1690,6 +1870,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1762,6 +1952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1814,6 +2014,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1871,6 +2081,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1923,6 +2143,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -1995,6 +2225,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2047,6 +2287,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2119,6 +2369,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2171,6 +2431,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2243,6 +2513,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2295,6 +2575,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2367,6 +2657,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2419,6 +2719,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2491,6 +2801,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2543,6 +2863,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2615,6 +2945,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2667,6 +3007,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2739,6 +3089,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2791,6 +3151,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2848,6 +3218,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2900,6 +3280,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -2972,6 +3362,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3024,6 +3424,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3096,6 +3506,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3148,6 +3568,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3220,6 +3650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3272,6 +3712,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3344,6 +3794,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3396,6 +3856,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3468,6 +3938,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3520,6 +4000,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3592,6 +4082,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3664,6 +4164,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3716,6 +4226,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3788,6 +4308,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3840,6 +4370,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3912,6 +4452,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -3964,6 +4514,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4036,6 +4596,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4088,6 +4658,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4160,6 +4740,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4212,6 +4802,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4284,6 +4884,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4336,6 +4946,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4408,6 +5028,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4460,6 +5090,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4532,6 +5172,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4584,6 +5234,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4656,6 +5316,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4708,6 +5378,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4780,6 +5460,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4832,6 +5522,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4904,6 +5604,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -4956,6 +5666,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5028,6 +5748,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5080,6 +5810,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5152,6 +5892,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5224,6 +5974,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5276,6 +6036,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5348,6 +6118,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5400,6 +6180,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5457,6 +6247,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5509,6 +6309,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5581,6 +6391,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5633,6 +6453,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5705,6 +6535,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5757,6 +6597,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5829,6 +6679,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5881,6 +6741,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -5953,6 +6823,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6005,6 +6885,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6077,6 +6967,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6129,6 +7029,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6201,6 +7111,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6253,6 +7173,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6325,6 +7255,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6377,6 +7317,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6449,6 +7399,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6501,6 +7461,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6573,6 +7543,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6625,6 +7605,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6682,6 +7672,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6734,6 +7734,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6806,6 +7816,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6858,6 +7878,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6930,6 +7960,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -6982,6 +8022,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7054,6 +8104,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7106,6 +8166,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7178,6 +8248,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7230,6 +8310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7302,6 +8392,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7354,6 +8454,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7426,6 +8536,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7478,6 +8598,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M114" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7550,6 +8680,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M115" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7602,6 +8742,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M116" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7674,6 +8824,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M117" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7726,6 +8886,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M118" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7798,6 +8968,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M119" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7850,6 +9030,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M120" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7907,6 +9097,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -7959,6 +9159,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8031,6 +9241,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8083,6 +9303,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8155,6 +9385,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8227,6 +9467,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M126" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8279,6 +9529,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8351,6 +9611,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8423,6 +9693,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8475,6 +9755,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8547,6 +9837,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8599,6 +9899,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8671,6 +9981,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8743,6 +10063,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M134" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8795,6 +10125,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M135" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8867,6 +10207,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M136" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8919,6 +10269,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M137" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -8991,6 +10351,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M138" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9063,6 +10433,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M139" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9115,6 +10495,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M140" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9187,6 +10577,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M141" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9239,6 +10639,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9311,6 +10721,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M143" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9363,6 +10783,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M144" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9435,6 +10865,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M145" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9487,6 +10927,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9544,6 +10994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M147" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9596,6 +11056,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M148" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9653,6 +11123,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M149" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9710,6 +11190,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9762,6 +11252,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M151" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9834,6 +11334,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M152" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9886,6 +11396,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M153" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -9958,6 +11478,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10010,6 +11540,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10082,6 +11622,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10134,6 +11684,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10206,6 +11766,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10258,6 +11828,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10330,6 +11910,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10382,6 +11972,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10454,6 +12054,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10506,6 +12116,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10578,6 +12198,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10630,6 +12260,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10702,6 +12342,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10754,6 +12404,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10826,6 +12486,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10878,6 +12548,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -10950,6 +12630,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11002,6 +12692,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11074,6 +12774,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11126,6 +12836,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11198,6 +12918,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11250,6 +12980,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11322,6 +13062,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11374,6 +13124,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M177" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11446,6 +13206,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M178" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11518,6 +13288,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M179" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11570,6 +13350,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M180" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11642,6 +13432,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M181" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11694,6 +13494,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M182" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11751,6 +13561,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M183" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11803,6 +13623,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11860,6 +13690,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11912,6 +13752,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -11984,6 +13834,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12036,6 +13896,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12108,6 +13978,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12160,6 +14040,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12232,6 +14122,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12284,6 +14184,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12356,6 +14266,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12408,6 +14328,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12480,6 +14410,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12532,6 +14472,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12604,6 +14554,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12656,6 +14616,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12728,6 +14698,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12780,6 +14760,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12852,6 +14842,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12904,6 +14904,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -12976,6 +14986,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13028,6 +15048,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13100,6 +15130,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13152,6 +15192,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13224,6 +15274,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13276,6 +15336,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13348,6 +15418,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13400,6 +15480,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13472,6 +15562,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13524,6 +15624,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13596,6 +15706,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13648,6 +15768,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13720,6 +15850,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13772,6 +15912,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13844,6 +15994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13896,6 +16056,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -13968,6 +16138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14020,6 +16200,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14092,6 +16282,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14144,6 +16344,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14216,6 +16426,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14268,6 +16488,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M224" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14340,6 +16570,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14392,6 +16632,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M226" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14464,6 +16714,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14516,6 +16776,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M228" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14588,6 +16858,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M229" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14640,6 +16920,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M230" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14712,6 +17002,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M231" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14764,6 +17064,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M232" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14836,6 +17146,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M233" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14888,6 +17208,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -14960,6 +17290,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M235" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15012,6 +17352,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M236" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15084,6 +17434,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15136,6 +17496,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15208,6 +17578,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15260,6 +17640,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15332,6 +17722,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15384,6 +17784,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15456,6 +17866,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15508,6 +17928,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15580,6 +18010,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15632,6 +18072,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15689,6 +18139,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15741,6 +18201,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15813,6 +18283,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15865,6 +18345,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M250" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15937,6 +18427,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -15989,6 +18489,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16061,6 +18571,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16113,6 +18633,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16185,6 +18715,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16237,6 +18777,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M256" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16309,6 +18859,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16381,6 +18941,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16433,6 +19003,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16505,6 +19085,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16557,6 +19147,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16629,6 +19229,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16681,6 +19291,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16753,6 +19373,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16805,6 +19435,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16877,6 +19517,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -16929,6 +19579,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17001,6 +19661,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17053,6 +19723,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17125,6 +19805,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17177,6 +19867,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17249,6 +19949,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17301,6 +20011,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17373,6 +20093,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17425,6 +20155,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17497,6 +20237,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17549,6 +20299,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17621,6 +20381,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17673,6 +20443,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17745,6 +20525,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17797,6 +20587,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17869,6 +20669,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17921,6 +20731,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -17993,6 +20813,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18045,6 +20875,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18102,6 +20942,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18154,6 +21004,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18226,6 +21086,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18278,6 +21148,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18350,6 +21230,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18402,6 +21292,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18474,6 +21374,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18526,6 +21436,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18598,6 +21518,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18650,6 +21580,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18722,6 +21662,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18774,6 +21724,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18846,6 +21806,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18898,6 +21868,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -18970,6 +21950,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19022,6 +22012,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19094,6 +22094,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19146,6 +22156,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19218,6 +22238,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19270,6 +22300,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19342,6 +22382,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19394,6 +22444,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19466,6 +22526,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19518,6 +22588,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19590,6 +22670,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19642,6 +22732,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19714,6 +22814,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19766,6 +22876,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19838,6 +22958,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19910,6 +23040,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -19962,6 +23102,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20034,6 +23184,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M317" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20086,6 +23246,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M318" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20158,6 +23328,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M319" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20210,6 +23390,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M320" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20282,6 +23472,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M321" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20334,6 +23534,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M322" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20406,6 +23616,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M323" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20478,6 +23698,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20530,6 +23760,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20602,6 +23842,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M326" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20654,6 +23904,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M327" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20726,6 +23986,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M328" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20798,6 +24068,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M329" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20850,6 +24130,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M330" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20922,6 +24212,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M331" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -20974,6 +24274,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M332" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21046,6 +24356,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M333" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21098,6 +24418,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M334" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21170,6 +24500,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M335" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21222,6 +24562,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M336" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21294,6 +24644,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M337" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21346,6 +24706,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M338" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21418,6 +24788,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M339" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21470,6 +24850,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M340" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21542,6 +24932,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M341" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21594,6 +24994,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M342" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21666,6 +25076,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M343" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21718,6 +25138,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M344" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21790,6 +25220,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M345" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21842,6 +25282,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M346" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21914,6 +25364,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -21966,6 +25426,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M348" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22023,6 +25493,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M349" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22075,6 +25555,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M350" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22147,6 +25637,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M351" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22199,6 +25699,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M352" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22271,6 +25781,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M353" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22323,6 +25843,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M354" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22395,6 +25925,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M355" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22447,6 +25987,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M356" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22504,6 +26054,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M357" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22556,6 +26116,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M358" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22628,6 +26198,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M359" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22680,6 +26260,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M360" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22737,6 +26327,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M361" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22789,6 +26389,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M362" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22861,6 +26471,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M363" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22913,6 +26533,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M364" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -22985,6 +26615,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M365" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23037,6 +26677,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M366" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23109,6 +26759,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M367" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23161,6 +26821,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M368" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23233,6 +26903,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23285,6 +26965,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M370" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23342,6 +27032,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M371" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23394,6 +27094,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M372" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23466,6 +27176,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M373" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23518,6 +27238,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M374" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23590,6 +27320,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M375" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23642,6 +27382,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M376" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23714,6 +27464,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M377" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23766,6 +27526,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M378" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23838,6 +27608,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M379" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23890,6 +27670,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M380" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -23962,6 +27752,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M381" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24014,6 +27814,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M382" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24086,6 +27896,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M383" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24138,6 +27958,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M384" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24195,6 +28025,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M385" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24247,6 +28087,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M386" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24319,6 +28169,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M387" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24371,6 +28231,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M388" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24443,6 +28313,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M389" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24495,6 +28375,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24567,6 +28457,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M391" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24619,6 +28519,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M392" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24691,6 +28601,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M393" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24743,6 +28663,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M394" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24815,6 +28745,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M395" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24867,6 +28807,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M396" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24939,6 +28889,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M397" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -24991,6 +28951,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M398" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25063,6 +29033,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M399" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25115,6 +29095,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M400" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25172,6 +29162,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M401" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25224,6 +29224,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M402" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25296,6 +29306,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M403" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25348,6 +29368,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M404" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25420,6 +29450,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M405" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25472,6 +29512,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M406" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25544,6 +29594,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M407" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25596,6 +29656,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M408" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25668,6 +29738,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M409" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25720,6 +29800,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M410" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25792,6 +29882,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M411" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25844,6 +29944,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M412" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25916,6 +30026,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M413" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -25968,6 +30088,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M414" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26040,6 +30170,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M415" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26092,6 +30232,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M416" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26164,6 +30314,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M417" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26216,6 +30376,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M418" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26288,6 +30458,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M419" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26340,6 +30520,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M420" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26412,6 +30602,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M421" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26464,6 +30664,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M422" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26536,6 +30746,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M423" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26588,6 +30808,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M424" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26660,6 +30890,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M425" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26712,6 +30952,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M426" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26784,6 +31034,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M427" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26836,6 +31096,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M428" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26908,6 +31178,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M429" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -26960,6 +31240,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M430" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27017,6 +31307,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M431" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27074,6 +31374,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M432" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27131,6 +31441,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M433" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27183,6 +31503,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M434" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27255,6 +31585,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M435" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27307,6 +31647,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M436" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27364,6 +31714,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M437" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27421,6 +31781,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M438" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27478,6 +31848,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M439" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27535,6 +31915,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M440" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27587,6 +31977,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M441" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27659,6 +32059,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M442" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27711,6 +32121,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M443" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27783,6 +32203,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M444" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27835,6 +32265,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M445" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27907,6 +32347,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M446" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -27959,6 +32409,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M447" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28031,6 +32491,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M448" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28083,6 +32553,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M449" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28140,6 +32620,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M450" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28197,6 +32687,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M451" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28254,6 +32754,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M452" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28306,6 +32816,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M453" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28378,6 +32898,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M454" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28430,6 +32960,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M455" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28502,6 +33042,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M456" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28554,6 +33104,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M457" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28611,6 +33171,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M458" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28663,6 +33233,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M459" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28720,6 +33300,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M460" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28777,6 +33367,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M461" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28829,6 +33429,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M462" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28886,6 +33496,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M463" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -28943,6 +33563,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M464" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29000,6 +33630,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M465" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29052,6 +33692,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M466" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29124,6 +33774,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M467" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29176,6 +33836,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M468" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29233,6 +33903,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M469" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29290,6 +33970,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M470" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29347,6 +34037,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M471" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29399,6 +34099,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M472" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29471,6 +34181,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M473" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29523,6 +34243,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M474" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29580,6 +34310,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M475" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29632,6 +34372,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M476" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29704,6 +34454,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M477" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29756,6 +34516,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M478" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29813,6 +34583,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M479" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29870,6 +34650,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M480" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29927,6 +34717,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M481" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -29979,6 +34779,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M482" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30051,6 +34861,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30103,6 +34923,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30175,6 +35005,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30227,6 +35067,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30284,6 +35134,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M487" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30341,6 +35201,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M488" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30393,6 +35263,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M489" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30450,6 +35330,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M490" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30507,6 +35397,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M491" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30564,6 +35464,16 @@
           <t>Acute</t>
         </is>
       </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
+        </is>
+      </c>
       <c r="M492" t="inlineStr">
         <is>
           <t>Gulf Coast Division</t>
@@ -30614,6 +35524,16 @@
       <c r="J493" t="inlineStr">
         <is>
           <t>Acute</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>COCKN</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>Meditech Expanse</t>
         </is>
       </c>
       <c r="M493" t="inlineStr">
